--- a/data/trans_dic/P25A$voluntad-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,36; 75,27</t>
+          <t>54,76; 74,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,11; 77,09</t>
+          <t>57,77; 76,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,14; 75,25</t>
+          <t>53,49; 74,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,26; 81,37</t>
+          <t>49,37; 80,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,51; 88,3</t>
+          <t>64,23; 88,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,36; 78,77</t>
+          <t>54,95; 79,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,65; 74,03</t>
+          <t>56,47; 73,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,61; 78,71</t>
+          <t>63,78; 78,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,69; 73,66</t>
+          <t>57,6; 72,9</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,09; 79,69</t>
+          <t>58,45; 79,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,39; 83,09</t>
+          <t>63,65; 83,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,47; 75,43</t>
+          <t>53,08; 74,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,59; 76,42</t>
+          <t>45,23; 75,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,58; 85,58</t>
+          <t>59,64; 84,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,82; 76,05</t>
+          <t>52,44; 76,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,37; 75,35</t>
+          <t>58,12; 75,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,47; 81,53</t>
+          <t>66,03; 81,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,1; 73,13</t>
+          <t>56,28; 72,48</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,04; 63,21</t>
+          <t>43,95; 63,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,2; 77,7</t>
+          <t>61,43; 77,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,44; 70,44</t>
+          <t>52,11; 70,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32,13; 73,6</t>
+          <t>32,2; 73,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,76; 94,21</t>
+          <t>68,84; 94,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,96; 100,0</t>
+          <t>45,98; 93,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,31; 63,12</t>
+          <t>44,84; 62,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,78; 79,04</t>
+          <t>65,14; 78,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,39; 72,24</t>
+          <t>54,91; 72,36</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,28; 58,97</t>
+          <t>46,88; 58,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,03; 71,8</t>
+          <t>61,35; 72,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,97; 63,36</t>
+          <t>50,45; 63,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,5; 83,34</t>
+          <t>61,47; 83,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,59; 84,52</t>
+          <t>66,64; 82,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,72; 87,4</t>
+          <t>68,97; 86,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,51; 61,96</t>
+          <t>51,36; 61,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,74; 73,85</t>
+          <t>64,53; 73,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,08; 68,16</t>
+          <t>57,48; 68,77</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,18; 64,59</t>
+          <t>40,52; 65,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,88; 68,67</t>
+          <t>49,35; 67,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,27; 68,73</t>
+          <t>49,87; 68,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,21; 79,41</t>
+          <t>46,93; 78,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,88; 91,62</t>
+          <t>71,24; 91,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,04; 75,65</t>
+          <t>52,52; 74,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,58; 66,5</t>
+          <t>47,42; 66,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,21; 74,81</t>
+          <t>59,95; 74,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,8; 68,39</t>
+          <t>53,25; 68,17</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,33; 100,0</t>
+          <t>31,23; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,76; 100,0</t>
+          <t>32,37; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,6; 100,0</t>
+          <t>17,32; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53,98; 79,45</t>
+          <t>53,52; 80,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57,24; 82,19</t>
+          <t>56,04; 80,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,9; 80,34</t>
+          <t>49,04; 80,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,84; 81,74</t>
+          <t>55,39; 80,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,86; 82,83</t>
+          <t>58,77; 81,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,34; 77,98</t>
+          <t>50,17; 77,84</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,68; 61,66</t>
+          <t>53,63; 61,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,17; 70,85</t>
+          <t>63,84; 70,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,39; 64,1</t>
+          <t>56,27; 64,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59,98; 72,58</t>
+          <t>60,04; 72,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,96; 81,6</t>
+          <t>72,3; 81,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,06; 74,58</t>
+          <t>64,58; 74,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,77; 63,52</t>
+          <t>57,01; 63,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,91; 73,2</t>
+          <t>67,61; 73,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,21; 66,87</t>
+          <t>60,24; 66,78</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53077; 72167</t>
+          <t>52499; 71832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65124; 86395</t>
+          <t>64740; 85873</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49605; 70248</t>
+          <t>49937; 69714</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19513; 30974</t>
+          <t>18795; 30804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33352; 45648</t>
+          <t>33204; 45644</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33987; 48364</t>
+          <t>33736; 48545</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77224; 99155</t>
+          <t>75634; 98316</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>104180; 128895</t>
+          <t>104456; 129009</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89279; 113990</t>
+          <t>89131; 112813</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47978; 63627</t>
+          <t>46668; 63812</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57002; 74713</t>
+          <t>57237; 74788</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38224; 54955</t>
+          <t>38670; 54396</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18446; 30920</t>
+          <t>18301; 30418</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31669; 46266</t>
+          <t>32238; 45798</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34687; 50900</t>
+          <t>35098; 51396</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69016; 90641</t>
+          <t>69923; 90291</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>95710; 117394</t>
+          <t>95073; 117436</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79815; 102232</t>
+          <t>78678; 101313</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46997; 67446</t>
+          <t>46892; 67409</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>100760; 125864</t>
+          <t>99511; 125233</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50553; 69227</t>
+          <t>51211; 69712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7833; 17940</t>
+          <t>7849; 17866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23478; 33133</t>
+          <t>24211; 33188</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6984; 13189</t>
+          <t>6065; 12322</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59394; 82734</t>
+          <t>58781; 82205</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>127725; 155835</t>
+          <t>128421; 155455</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59515; 80526</t>
+          <t>61207; 80663</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>128656; 160472</t>
+          <t>127579; 160284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>194659; 228995</t>
+          <t>195676; 229788</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>113813; 144292</t>
+          <t>114904; 144442</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38956; 52791</t>
+          <t>38936; 52809</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76474; 95629</t>
+          <t>75404; 93891</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60427; 75753</t>
+          <t>59779; 75353</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>172797; 207850</t>
+          <t>172304; 207701</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>279728; 319085</t>
+          <t>278838; 318255</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>179472; 214296</t>
+          <t>180720; 216216</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25550; 41073</t>
+          <t>25767; 41656</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>63415; 87309</t>
+          <t>62742; 85529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54133; 74013</t>
+          <t>53701; 73379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16403; 28188</t>
+          <t>16660; 27978</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49917; 63628</t>
+          <t>49475; 63313</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36533; 53105</t>
+          <t>36868; 52525</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46158; 65893</t>
+          <t>46981; 66131</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>120329; 147063</t>
+          <t>117856; 146311</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>95710; 121659</t>
+          <t>94726; 121264</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1732; 5527</t>
+          <t>1726; 5527</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1971; 6016</t>
+          <t>1947; 6016</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>980; 5570</t>
+          <t>965; 5570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26442; 38919</t>
+          <t>26220; 39513</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34882; 50083</t>
+          <t>34152; 49304</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18030; 29030</t>
+          <t>17720; 29155</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30440; 44562</t>
+          <t>30194; 44148</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40076; 55456</t>
+          <t>39348; 54280</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20578; 32524</t>
+          <t>20925; 32464</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>334782; 384515</t>
+          <t>334456; 381878</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>523706; 578177</t>
+          <t>520980; 577329</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>341428; 388135</t>
+          <t>340682; 387723</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150391; 181985</t>
+          <t>150536; 181390</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>280509; 313735</t>
+          <t>277983; 311917</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>214306; 249483</t>
+          <t>216048; 249057</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>496429; 555440</t>
+          <t>498527; 554296</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>815317; 878788</t>
+          <t>811643; 877509</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>566025; 628609</t>
+          <t>566306; 627755</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$voluntad-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,76; 74,92</t>
+          <t>55,45; 74,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,77; 76,62</t>
+          <t>57,0; 75,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,49; 74,68</t>
+          <t>53,35; 74,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,37; 80,92</t>
+          <t>50,65; 80,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,23; 88,29</t>
+          <t>67,16; 88,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,95; 79,07</t>
+          <t>55,47; 78,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,47; 73,4</t>
+          <t>57,01; 73,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,78; 78,78</t>
+          <t>63,68; 79,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,6; 72,9</t>
+          <t>56,45; 73,05</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,45; 79,93</t>
+          <t>59,39; 79,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,65; 83,17</t>
+          <t>63,73; 83,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,08; 74,66</t>
+          <t>52,5; 74,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,23; 75,18</t>
+          <t>44,96; 76,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,64; 84,72</t>
+          <t>59,73; 84,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,44; 76,79</t>
+          <t>52,8; 77,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,12; 75,05</t>
+          <t>57,62; 75,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,03; 81,56</t>
+          <t>66,22; 82,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,28; 72,48</t>
+          <t>56,89; 72,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,95; 63,17</t>
+          <t>43,83; 63,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,43; 77,31</t>
+          <t>60,84; 76,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,11; 70,93</t>
+          <t>51,27; 71,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32,2; 73,29</t>
+          <t>32,66; 71,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,84; 94,36</t>
+          <t>71,21; 95,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,98; 93,43</t>
+          <t>50,63; 93,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,84; 62,71</t>
+          <t>45,51; 62,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65,14; 78,85</t>
+          <t>65,15; 78,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,91; 72,36</t>
+          <t>54,22; 73,02</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,88; 58,9</t>
+          <t>47,08; 58,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,35; 72,05</t>
+          <t>61,38; 72,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,45; 63,42</t>
+          <t>49,58; 63,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,47; 83,37</t>
+          <t>61,47; 84,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,64; 82,98</t>
+          <t>66,35; 83,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,97; 86,94</t>
+          <t>69,66; 87,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,36; 61,91</t>
+          <t>51,0; 62,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,53; 73,66</t>
+          <t>64,47; 73,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,48; 68,77</t>
+          <t>57,2; 68,02</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,52; 65,51</t>
+          <t>41,34; 64,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,35; 67,27</t>
+          <t>49,82; 67,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,87; 68,14</t>
+          <t>49,45; 67,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,93; 78,82</t>
+          <t>45,54; 78,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,24; 91,17</t>
+          <t>72,77; 91,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,52; 74,83</t>
+          <t>51,88; 75,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,42; 66,74</t>
+          <t>46,92; 66,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,95; 74,43</t>
+          <t>60,51; 74,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,25; 68,17</t>
+          <t>54,08; 68,12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,23; 100,0</t>
+          <t>30,84; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,37; 100,0</t>
+          <t>31,56; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 100,0</t>
+          <t>17,29; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53,52; 80,66</t>
+          <t>52,71; 80,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,04; 80,91</t>
+          <t>58,69; 82,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,04; 80,68</t>
+          <t>46,77; 80,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,39; 80,98</t>
+          <t>56,02; 80,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58,77; 81,07</t>
+          <t>60,76; 82,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,17; 77,84</t>
+          <t>50,4; 78,07</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,63; 61,23</t>
+          <t>53,88; 61,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,84; 70,74</t>
+          <t>63,91; 70,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,27; 64,03</t>
+          <t>56,33; 63,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60,04; 72,34</t>
+          <t>60,06; 71,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,3; 81,13</t>
+          <t>72,88; 81,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,58; 74,45</t>
+          <t>64,54; 74,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,01; 63,39</t>
+          <t>56,59; 63,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,61; 73,09</t>
+          <t>67,79; 73,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,24; 66,78</t>
+          <t>60,18; 66,73</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52499; 71832</t>
+          <t>53165; 71315</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64740; 85873</t>
+          <t>63876; 84946</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49937; 69714</t>
+          <t>49802; 69612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18795; 30804</t>
+          <t>19279; 30823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33204; 45644</t>
+          <t>34720; 45785</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33736; 48545</t>
+          <t>34059; 48232</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75634; 98316</t>
+          <t>76365; 98567</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>104456; 129009</t>
+          <t>104289; 130345</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89131; 112813</t>
+          <t>87362; 113044</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46668; 63812</t>
+          <t>47416; 63806</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57237; 74788</t>
+          <t>57306; 74701</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38670; 54396</t>
+          <t>38249; 54270</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18301; 30418</t>
+          <t>18191; 30790</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32238; 45798</t>
+          <t>32290; 45813</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35098; 51396</t>
+          <t>35340; 51690</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69923; 90291</t>
+          <t>69319; 90534</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>95073; 117436</t>
+          <t>95341; 118184</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78678; 101313</t>
+          <t>79530; 102010</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46892; 67409</t>
+          <t>46773; 67441</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99511; 125233</t>
+          <t>98547; 124584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51211; 69712</t>
+          <t>50385; 70481</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7849; 17866</t>
+          <t>7960; 17476</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24211; 33188</t>
+          <t>25046; 33574</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6065; 12322</t>
+          <t>6678; 12388</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58781; 82205</t>
+          <t>59651; 81794</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>128421; 155455</t>
+          <t>128452; 155093</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61207; 80663</t>
+          <t>60445; 81393</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>127579; 160284</t>
+          <t>128124; 160399</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>195676; 229788</t>
+          <t>195767; 230435</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114904; 144442</t>
+          <t>112909; 144427</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38936; 52809</t>
+          <t>38934; 53307</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75404; 93891</t>
+          <t>75069; 94193</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59779; 75353</t>
+          <t>60381; 75885</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>172304; 207701</t>
+          <t>171103; 208245</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>278838; 318255</t>
+          <t>278582; 317472</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180720; 216216</t>
+          <t>179844; 213877</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25767; 41656</t>
+          <t>26289; 40929</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62742; 85529</t>
+          <t>63341; 86215</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53701; 73379</t>
+          <t>53259; 73018</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16660; 27978</t>
+          <t>16166; 27843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49475; 63313</t>
+          <t>50534; 63505</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36868; 52525</t>
+          <t>36418; 52841</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46981; 66131</t>
+          <t>46488; 66054</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>117856; 146311</t>
+          <t>118961; 146312</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>94726; 121264</t>
+          <t>96202; 121172</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1726; 5527</t>
+          <t>1704; 5527</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1947; 6016</t>
+          <t>1899; 6016</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>965; 5570</t>
+          <t>963; 5570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26220; 39513</t>
+          <t>25823; 39352</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34152; 49304</t>
+          <t>35766; 50047</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17720; 29155</t>
+          <t>16899; 29022</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30194; 44148</t>
+          <t>30538; 43706</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39348; 54280</t>
+          <t>40679; 55235</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20925; 32464</t>
+          <t>21020; 32559</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>334456; 381878</t>
+          <t>336046; 384548</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>520980; 577329</t>
+          <t>521546; 576324</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>340682; 387723</t>
+          <t>341105; 387069</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150536; 181390</t>
+          <t>150598; 180176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>277983; 311917</t>
+          <t>280206; 313565</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>216048; 249057</t>
+          <t>215916; 249567</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>498527; 554296</t>
+          <t>494838; 553777</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>811643; 877509</t>
+          <t>813849; 879761</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>566306; 627755</t>
+          <t>565670; 627268</t>
         </is>
       </c>
     </row>
